--- a/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20260307.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20260307.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,69 @@
       </c>
       <c r="E2" t="n">
         <v>66.78</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>8808606CS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Torani - Caramel Sauce</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>72.69</v>
+      </c>
+      <c r="E3" t="n">
+        <v>290.76</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>8808605CS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Torani - Dark Chocolate Sauce</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>67.89</v>
+      </c>
+      <c r="E4" t="n">
+        <v>543.12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>8808604CS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Torani - White Chocolate Sauce</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>71.09</v>
+      </c>
+      <c r="E5" t="n">
+        <v>142.18</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20260307.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20260307.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,111 @@
         <v>142.18</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3639225768</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Compound - Raspberry</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>72.48999999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>72.48999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>63204854</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Degreaser - for Panini Press (Dawn)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>92.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>433SLINERBL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sheet Pan Liner - Silicone Coated</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>384.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>150BB4224N</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bag Paper - Baguette</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>118.99</v>
+      </c>
+      <c r="E9" t="n">
+        <v>237.98</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>433qlinerbl</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sheet Pan Liner - White</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="E10" t="n">
+        <v>187.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
